--- a/Project/wave 2 capstone for trainees.xlsx
+++ b/Project/wave 2 capstone for trainees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE240DAB-CA6E-4CD4-B804-32068A4A51CE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8AA301-4849-4D8D-9C3E-1D487FB1ED8B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{1D142583-5EB2-4B24-841E-90261AB3BE14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{1D142583-5EB2-4B24-841E-90261AB3BE14}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Batch with projects" sheetId="2" r:id="rId1"/>
@@ -1265,7 +1265,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5643B20D-A0CB-4F30-935F-4ED657CF55DB}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1403,7 +1402,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>2</v>
       </c>
@@ -1434,7 +1433,7 @@
 User – view audio details, search, view rating, add rating</v>
       </c>
     </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -1461,7 +1460,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>2</v>
       </c>
@@ -1591,7 +1590,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -1622,7 +1621,7 @@
 User list doctors/Search/Rate/book appointment</v>
       </c>
     </row>
-    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>4</v>
       </c>
@@ -1649,7 +1648,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>4</v>
       </c>
@@ -1774,7 +1773,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>6</v>
       </c>
@@ -1807,7 +1806,7 @@
 3. User can Book/View/Cancel the tickets/ search bus</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>6</v>
       </c>
@@ -1834,7 +1833,7 @@
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>6</v>
       </c>
@@ -1955,7 +1954,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>8</v>
       </c>
@@ -1986,7 +1985,7 @@
 User can view the products ,add products to the cart and delete the product from the cart and rate product</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>8</v>
       </c>
@@ -2013,7 +2012,7 @@
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>8</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>10</v>
       </c>
@@ -2167,7 +2166,7 @@
 The Kitchen staff should be able to see the order assingned to them, update the order status, search the order </v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>10</v>
       </c>
@@ -2194,7 +2193,7 @@
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>10</v>
       </c>
@@ -2315,7 +2314,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>12</v>
       </c>
@@ -2348,7 +2347,7 @@
  The user should be able to view all the Bugs raised under his name and Bugs in a Project​</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -2375,7 +2374,7 @@
       </c>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>12</v>
       </c>
@@ -2402,7 +2401,7 @@
       </c>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>13</v>
       </c>
@@ -2433,7 +2432,7 @@
 User​ - Search Book/List Book/rate book/view book ratings</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>13</v>
       </c>
@@ -2460,7 +2459,7 @@
       </c>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>13</v>
       </c>
@@ -2581,7 +2580,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>15</v>
       </c>
@@ -2612,7 +2611,7 @@
 User – view audio details, search, view rating, add rating</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>15</v>
       </c>
@@ -2639,7 +2638,7 @@
       </c>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>15</v>
       </c>
@@ -2760,7 +2759,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>17</v>
       </c>
@@ -2791,7 +2790,7 @@
 User list doctors/Search/Rate/book appointment</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>17</v>
       </c>
@@ -2818,7 +2817,7 @@
       </c>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>17</v>
       </c>
@@ -2940,7 +2939,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>19</v>
       </c>
@@ -2973,7 +2972,7 @@
 3. User can Book/View/Cancel the tickets/ search bus</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>19</v>
       </c>
@@ -3000,7 +2999,7 @@
       </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>19</v>
       </c>
@@ -3121,7 +3120,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>21</v>
       </c>
@@ -3152,7 +3151,7 @@
 User can view the products ,add products to the cart and delete the product from the cart and rate product</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>21</v>
       </c>
@@ -3179,7 +3178,7 @@
       </c>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>21</v>
       </c>
@@ -3222,13 +3221,6 @@
       <c r="H76" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J64" xr:uid="{F3E81DC8-8185-412D-9521-A4B895F36CCF}">
-    <filterColumn colId="9">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3236,7 +3228,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BAEE111-1C0F-4A96-9FD2-A746B422C8A8}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3267,7 +3258,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>190</v>
       </c>
@@ -3289,7 +3280,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>190</v>
       </c>
@@ -3311,7 +3302,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>190</v>
       </c>
@@ -3333,7 +3324,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>190</v>
       </c>
@@ -3355,7 +3346,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>190</v>
       </c>
@@ -3377,7 +3368,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -3399,7 +3390,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>190</v>
       </c>
@@ -3410,7 +3401,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="6" t="s">
         <v>179</v>
@@ -3423,13 +3414,6 @@
       <c r="A17" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C16" xr:uid="{446B5035-3E8A-490A-8827-1A7E69C1A259}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Jagadeesh"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Project/wave 2 capstone for trainees.xlsx
+++ b/Project/wave 2 capstone for trainees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8AA301-4849-4D8D-9C3E-1D487FB1ED8B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3D840B-7AE2-4DD2-8D1E-F42376915DBB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{1D142583-5EB2-4B24-841E-90261AB3BE14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{1D142583-5EB2-4B24-841E-90261AB3BE14}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Batch with projects" sheetId="2" r:id="rId1"/>
@@ -1265,6 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5643B20D-A0CB-4F30-935F-4ED657CF55DB}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1402,7 +1403,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>2</v>
       </c>
@@ -1433,7 +1434,7 @@
 User – view audio details, search, view rating, add rating</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -1460,7 +1461,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>2</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -1621,7 +1622,7 @@
 User list doctors/Search/Rate/book appointment</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>4</v>
       </c>
@@ -1648,7 +1649,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>4</v>
       </c>
@@ -1773,7 +1774,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>6</v>
       </c>
@@ -1806,7 +1807,7 @@
 3. User can Book/View/Cancel the tickets/ search bus</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>6</v>
       </c>
@@ -1833,7 +1834,7 @@
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>6</v>
       </c>
@@ -1954,7 +1955,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>8</v>
       </c>
@@ -1985,7 +1986,7 @@
 User can view the products ,add products to the cart and delete the product from the cart and rate product</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>8</v>
       </c>
@@ -2012,7 +2013,7 @@
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>8</v>
       </c>
@@ -2134,7 +2135,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>10</v>
       </c>
@@ -2166,7 +2167,7 @@
 The Kitchen staff should be able to see the order assingned to them, update the order status, search the order </v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>10</v>
       </c>
@@ -2193,7 +2194,7 @@
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>10</v>
       </c>
@@ -2314,7 +2315,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>12</v>
       </c>
@@ -2347,7 +2348,7 @@
  The user should be able to view all the Bugs raised under his name and Bugs in a Project​</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -2374,7 +2375,7 @@
       </c>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>12</v>
       </c>
@@ -2401,7 +2402,7 @@
       </c>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>13</v>
       </c>
@@ -2432,7 +2433,7 @@
 User​ - Search Book/List Book/rate book/view book ratings</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>13</v>
       </c>
@@ -2459,7 +2460,7 @@
       </c>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>13</v>
       </c>
@@ -2580,7 +2581,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>15</v>
       </c>
@@ -2611,7 +2612,7 @@
 User – view audio details, search, view rating, add rating</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>15</v>
       </c>
@@ -2638,7 +2639,7 @@
       </c>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>15</v>
       </c>
@@ -2759,7 +2760,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>17</v>
       </c>
@@ -2790,7 +2791,7 @@
 User list doctors/Search/Rate/book appointment</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>17</v>
       </c>
@@ -2817,7 +2818,7 @@
       </c>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>17</v>
       </c>
@@ -2939,7 +2940,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>19</v>
       </c>
@@ -2972,7 +2973,7 @@
 3. User can Book/View/Cancel the tickets/ search bus</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>19</v>
       </c>
@@ -2999,7 +3000,7 @@
       </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>19</v>
       </c>
@@ -3120,7 +3121,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>21</v>
       </c>
@@ -3151,7 +3152,7 @@
 User can view the products ,add products to the cart and delete the product from the cart and rate product</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>21</v>
       </c>
@@ -3178,7 +3179,7 @@
       </c>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>21</v>
       </c>
@@ -3221,6 +3222,13 @@
       <c r="H76" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J64" xr:uid="{045786C5-3FA0-454F-9CC5-B0DAD19770E5}">
+    <filterColumn colId="9">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Project/wave 2 capstone for trainees.xlsx
+++ b/Project/wave 2 capstone for trainees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch1_Apr2023\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3D840B-7AE2-4DD2-8D1E-F42376915DBB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4286B0-F194-4F42-A6EE-4C9C11D6B763}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{1D142583-5EB2-4B24-841E-90261AB3BE14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{1D142583-5EB2-4B24-841E-90261AB3BE14}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Batch with projects" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="211">
   <si>
     <t>reenu.rachelthomas@ust.com</t>
   </si>
@@ -687,6 +687,9 @@
   </si>
   <si>
     <t>JAG</t>
+  </si>
+  <si>
+    <t>YES</t>
   </si>
 </sst>
 </file>
@@ -801,7 +804,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -876,11 +879,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -951,6 +963,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3428,7 +3443,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367B47E6-B433-4A99-BA12-F3C635D6BE01}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
@@ -3437,7 +3452,7 @@
     <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>191</v>
       </c>
@@ -3451,7 +3466,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -3464,8 +3479,11 @@
       <c r="D2" s="16" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E2" s="26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -3479,7 +3497,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -3492,8 +3510,11 @@
       <c r="D4" s="16" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -3506,8 +3527,11 @@
       <c r="D5" s="16" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -3521,7 +3545,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -3535,7 +3559,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -3549,7 +3573,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -3563,7 +3587,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
     </row>
   </sheetData>
